--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484129_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484129_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2084</v>
+        <v>3.1968</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3976</v>
+        <v>4.358</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.1892</v>
+        <v>-1.1612</v>
       </c>
       <c r="G2" t="n">
         <v>2.8222</v>
@@ -610,13 +610,13 @@
         <v>1.5871</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.4154</v>
+        <v>-1.427</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1926</v>
+        <v>-0.2323</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.2227</v>
+        <v>-1.1947</v>
       </c>
       <c r="V2" t="n">
         <v>1.2065</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. ESONO MBA</t>
+          <t>I. VILLAR CANTERO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9147999999999999</v>
+        <v>0.1876</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.3754</v>
+        <v>1.9275</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2902</v>
+        <v>-1.7399</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.0392</v>
+        <v>2.6711</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.0612</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.978</v>
+        <v>1.7139</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.403</v>
+        <v>4.1615</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.6038</v>
+        <v>1.6638</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2008</v>
+        <v>2.4977</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.6362</v>
+        <v>-1.4904</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.4573</v>
+        <v>-0.7067</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.1788</v>
+        <v>-0.7837</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5952</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9838</v>
+        <v>-2.9758</v>
       </c>
       <c r="R3" t="n">
-        <v>2.579</v>
+        <v>1.5871</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6726</v>
+        <v>-2.3013</v>
       </c>
       <c r="T3" t="n">
-        <v>0.805</v>
+        <v>-0.4647</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8676</v>
+        <v>-1.8366</v>
       </c>
       <c r="V3" t="n">
-        <v>1.6863</v>
+        <v>1.2065</v>
       </c>
       <c r="W3" t="n">
         <v>1.2065</v>
       </c>
       <c r="X3" t="n">
-        <v>0.4798</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0176</v>
+        <v>0.0921</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0974</v>
+        <v>1.4035</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.115</v>
+        <v>-1.3114</v>
       </c>
       <c r="G4" t="n">
         <v>2.6685</v>
@@ -766,13 +766,13 @@
         <v>1.1903</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.4039</v>
+        <v>-2.2942</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1109</v>
+        <v>-0.8048</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.2931</v>
+        <v>-1.4895</v>
       </c>
       <c r="V4" t="n">
         <v>-1.4724</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. VILLAR CANTERO</t>
+          <t>A. BELTRAN MATA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.7318</v>
+        <v>-0.6889999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>1.457</v>
+        <v>-0.0707</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.1888</v>
+        <v>-0.6183</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6711</v>
+        <v>0.6736</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9572000000000001</v>
+        <v>-3.0187</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7139</v>
+        <v>3.6923</v>
       </c>
       <c r="J5" t="n">
-        <v>4.1615</v>
+        <v>1.1147</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6638</v>
+        <v>-2.0204</v>
       </c>
       <c r="L5" t="n">
-        <v>2.4977</v>
+        <v>3.1352</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4904</v>
+        <v>-0.4412</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7067</v>
+        <v>-0.9983</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7837</v>
+        <v>0.5572</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.3887</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9758</v>
+        <v>-1.9838</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5871</v>
+        <v>0.9919</v>
       </c>
       <c r="S5" t="n">
-        <v>-3.2207</v>
+        <v>-1.5772</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9352</v>
+        <v>-0.408</v>
       </c>
       <c r="U5" t="n">
-        <v>-2.2855</v>
+        <v>-1.1691</v>
       </c>
       <c r="V5" t="n">
         <v>1.2065</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. BELTRAN MATA</t>
+          <t>J. ESONO MBA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0895</v>
+        <v>-1.173</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2747</v>
+        <v>-1.5374</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8147</v>
+        <v>0.3643</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6736</v>
+        <v>-3.0392</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.0187</v>
+        <v>-2.0612</v>
       </c>
       <c r="I6" t="n">
-        <v>3.6923</v>
+        <v>-0.978</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1147</v>
+        <v>-0.403</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.0204</v>
+        <v>-0.6038</v>
       </c>
       <c r="L6" t="n">
-        <v>3.1352</v>
+        <v>0.2008</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4412</v>
+        <v>-2.6362</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9983</v>
+        <v>-1.4573</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5572</v>
+        <v>-1.1788</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.9919</v>
+        <v>0.5952</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9919</v>
+        <v>2.579</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.9776</v>
+        <v>-0.4152</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6121</v>
+        <v>-0.357</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.3655</v>
+        <v>-0.0583</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2065</v>
+        <v>1.6863</v>
       </c>
       <c r="W6" t="n">
         <v>1.2065</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.4798</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4096</v>
+        <v>-1.2809</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6011</v>
+        <v>1.5614</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.0107</v>
+        <v>-2.8423</v>
       </c>
       <c r="G7" t="n">
         <v>1.5806</v>
@@ -1000,13 +1000,13 @@
         <v>1.1903</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3275</v>
+        <v>-1.1988</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4307</v>
+        <v>-0.4704</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8968</v>
+        <v>-0.7285</v>
       </c>
       <c r="V7" t="n">
         <v>-0.8692</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1452</v>
+        <v>-1.8749</v>
       </c>
       <c r="E8" t="n">
-        <v>1.3781</v>
+        <v>1.4801</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.5233</v>
+        <v>-3.355</v>
       </c>
       <c r="G8" t="n">
         <v>1.2211</v>
@@ -1078,13 +1078,13 @@
         <v>1.3887</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3502</v>
+        <v>-1.0798</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3741</v>
+        <v>-0.272</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9761</v>
+        <v>-0.8078</v>
       </c>
       <c r="V8" t="n">
         <v>-2.4129</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3274</v>
+        <v>-2.107</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6488</v>
+        <v>0.8132</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.9763</v>
+        <v>-2.9202</v>
       </c>
       <c r="G9" t="n">
         <v>1.3688</v>
@@ -1156,13 +1156,13 @@
         <v>0.1984</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1642</v>
+        <v>-0.9438</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2494</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9149</v>
+        <v>-0.8588</v>
       </c>
       <c r="V9" t="n">
         <v>-1.7384</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. CRUZ JOBACHO</t>
+          <t>M. GARCIA IBAÑEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5613</v>
+        <v>-2.3323</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5991</v>
+        <v>-2.1666</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9623</v>
+        <v>-0.1657</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0346</v>
+        <v>0.5259</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4387</v>
+        <v>-1.069</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5959</v>
+        <v>1.5949</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2114</v>
+        <v>0.1459</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0106</v>
+        <v>-0.6197</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2008</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.246</v>
+        <v>0.38</v>
       </c>
       <c r="N10" t="n">
         <v>-0.4493</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7967</v>
+        <v>0.8292</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1984</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1903</v>
+        <v>0.9919</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1932</v>
+        <v>-1.8663</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1814</v>
+        <v>-0.3287</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.3746</v>
+        <v>-1.5376</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.532</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. GARCIA IBAÑEZ</t>
+          <t>A. CRUZ JOBACHO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9368</v>
+        <v>-2.8037</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5747</v>
+        <v>-0.7010999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3621</v>
+        <v>-2.1025</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5259</v>
+        <v>-1.0346</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.069</v>
+        <v>-0.4387</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5949</v>
+        <v>-0.5959</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1459</v>
+        <v>0.2114</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6197</v>
+        <v>0.0106</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7655999999999999</v>
+        <v>0.2008</v>
       </c>
       <c r="M11" t="n">
-        <v>0.38</v>
+        <v>-1.246</v>
       </c>
       <c r="N11" t="n">
         <v>-0.4493</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8292</v>
+        <v>-0.7967</v>
       </c>
       <c r="P11" t="n">
+        <v>0.1984</v>
+      </c>
+      <c r="Q11" t="n">
         <v>-0.9919</v>
       </c>
-      <c r="Q11" t="n">
-        <v>-1.9838</v>
-      </c>
       <c r="R11" t="n">
-        <v>0.9919</v>
+        <v>1.1903</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.4708</v>
+        <v>-1.4355</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7368</v>
+        <v>0.0794</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.734</v>
+        <v>-1.5149</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.532</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.096</v>
+        <v>-8.7843</v>
       </c>
       <c r="E12" t="n">
-        <v>6.7561</v>
+        <v>7.067899999999999</v>
       </c>
       <c r="F12" t="n">
         <v>-15.8522</v>
@@ -1372,7 +1372,7 @@
         <v>14.5742</v>
       </c>
       <c r="M12" t="n">
-        <v>-9.002099999999999</v>
+        <v>-9.0021</v>
       </c>
       <c r="N12" t="n">
         <v>-7.1892</v>
@@ -1390,13 +1390,13 @@
         <v>12.895</v>
       </c>
       <c r="S12" t="n">
-        <v>-14.8509</v>
+        <v>-14.5391</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.6554</v>
+        <v>-3.3435</v>
       </c>
       <c r="U12" t="n">
-        <v>-11.1956</v>
+        <v>-11.1958</v>
       </c>
       <c r="V12" t="n">
         <v>-1.7191</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.416700000000001</v>
+        <v>7.7315</v>
       </c>
       <c r="E13" t="n">
-        <v>7.1359</v>
+        <v>5.7075</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2807</v>
+        <v>2.024</v>
       </c>
       <c r="G13" t="n">
         <v>0.7027</v>
@@ -1468,13 +1468,13 @@
         <v>1.7855</v>
       </c>
       <c r="S13" t="n">
-        <v>4.6581</v>
+        <v>2.973</v>
       </c>
       <c r="T13" t="n">
-        <v>3.6675</v>
+        <v>2.239</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9907</v>
+        <v>0.7339</v>
       </c>
       <c r="V13" t="n">
         <v>2.2704</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.5603</v>
+        <v>4.311</v>
       </c>
       <c r="E14" t="n">
-        <v>3.3773</v>
+        <v>4.9077</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8169999999999999</v>
+        <v>-0.5968</v>
       </c>
       <c r="G14" t="n">
         <v>1.5127</v>
@@ -1546,13 +1546,13 @@
         <v>2.3806</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2897</v>
+        <v>1.461</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6008</v>
+        <v>0.9297</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3111</v>
+        <v>0.5313</v>
       </c>
       <c r="V14" t="n">
         <v>0.9405</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4334</v>
+        <v>3.316</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4927</v>
+        <v>4.2069</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0593</v>
+        <v>-0.891</v>
       </c>
       <c r="G15" t="n">
         <v>-0.4456</v>
@@ -1624,13 +1624,13 @@
         <v>1.5871</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7323</v>
+        <v>0.1502</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8105</v>
+        <v>-0.0963</v>
       </c>
       <c r="U15" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.2465</v>
       </c>
       <c r="V15" t="n">
         <v>3.0162</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. HALL</t>
+          <t>D. FERNANDEZ LINARES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.191</v>
+        <v>1.6947</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1913</v>
+        <v>0.0189</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0003</v>
+        <v>1.6758</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3058</v>
+        <v>-1.9244</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7008</v>
+        <v>0.7458</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.0066</v>
+        <v>-2.6702</v>
       </c>
       <c r="J16" t="n">
-        <v>2.8908</v>
+        <v>-0.8258</v>
       </c>
       <c r="K16" t="n">
-        <v>2.1679</v>
+        <v>0.5295</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7229</v>
+        <v>-1.3553</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.1966</v>
+        <v>-1.0986</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4671</v>
+        <v>0.2163</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.7295</v>
+        <v>-1.3149</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1984</v>
+        <v>0.9919</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1903</v>
+        <v>1.9838</v>
       </c>
       <c r="S16" t="n">
-        <v>2.2984</v>
+        <v>2.29</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2924</v>
+        <v>1.8366</v>
       </c>
       <c r="U16" t="n">
-        <v>1.006</v>
+        <v>0.4534</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.3373</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.3373</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. SENGHOR</t>
+          <t>S. HALL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3821</v>
+        <v>1.158</v>
       </c>
       <c r="E17" t="n">
-        <v>3.9114</v>
+        <v>2.5791</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.5293</v>
+        <v>-1.4211</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0033</v>
+        <v>-0.3058</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8517</v>
+        <v>0.7008</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1516</v>
+        <v>-1.0066</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6558</v>
+        <v>2.8908</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9731</v>
+        <v>2.1679</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6827</v>
+        <v>0.7229</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6525</v>
+        <v>-3.1966</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1214</v>
+        <v>-1.4671</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5312</v>
+        <v>-1.7295</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3968</v>
+        <v>0.1984</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3968</v>
+        <v>1.1903</v>
       </c>
       <c r="S17" t="n">
-        <v>2.129</v>
+        <v>1.2654</v>
       </c>
       <c r="T17" t="n">
-        <v>1.9896</v>
+        <v>0.6803</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1394</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.1469</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.4129</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. LORAS MONTERO</t>
+          <t>A. SENGHOR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1662</v>
+        <v>0.826</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0669</v>
+        <v>3.2992</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9006999999999999</v>
+        <v>-2.4732</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.4128</v>
+        <v>1.0033</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8606</v>
+        <v>0.8517</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.5522</v>
+        <v>0.1516</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2374</v>
+        <v>1.6558</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2048</v>
+        <v>0.9731</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0325</v>
+        <v>0.6827</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.1755</v>
+        <v>-0.6525</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6558</v>
+        <v>-0.1214</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.5197</v>
+        <v>-0.5312</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.3806</v>
+        <v>0.3968</v>
       </c>
       <c r="Q18" t="n">
-        <v>-4.9596</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.579</v>
+        <v>0.3968</v>
       </c>
       <c r="S18" t="n">
-        <v>5.2329</v>
+        <v>1.5729</v>
       </c>
       <c r="T18" t="n">
-        <v>4.3307</v>
+        <v>1.3774</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9023</v>
+        <v>0.1955</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7267</v>
+        <v>-2.1469</v>
       </c>
       <c r="W18" t="n">
-        <v>1.9331</v>
+        <v>0.266</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2065</v>
+        <v>-2.4129</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ LINARES</t>
+          <t>J. CAMPENY LLOVERAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0738</v>
+        <v>0.0363</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6136</v>
+        <v>1.4566</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5398</v>
+        <v>-1.4203</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.9244</v>
+        <v>0.7449</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7458</v>
+        <v>-0.6452</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.6702</v>
+        <v>1.3901</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.8258</v>
+        <v>1.9384</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5295</v>
+        <v>0.6908</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.3553</v>
+        <v>1.2476</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0986</v>
+        <v>-1.1934</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2163</v>
+        <v>-1.336</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.3149</v>
+        <v>0.1425</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9919</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9838</v>
+        <v>0.9919</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5215</v>
+        <v>0.7638</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2041</v>
+        <v>0.5102</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3173</v>
+        <v>0.2536</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3373</v>
+        <v>-1.4724</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3373</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. CAMPENY LLOVERAS</t>
+          <t>T. KOHAN LÓPEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3642</v>
+        <v>-0.7096</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2526</v>
+        <v>0.3163</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6167</v>
+        <v>-1.0259</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7449</v>
+        <v>-1.1517</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6452</v>
+        <v>0.7203000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3901</v>
+        <v>-1.872</v>
       </c>
       <c r="J20" t="n">
-        <v>1.9384</v>
+        <v>0.1008</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6908</v>
+        <v>0.1008</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2476</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1934</v>
+        <v>-1.2525</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.336</v>
+        <v>0.6195000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1425</v>
+        <v>-1.872</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9919</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3634</v>
+        <v>0.4421</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3061</v>
+        <v>0.2154</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0572</v>
+        <v>0.2267</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.4724</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.4724</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7851</v>
+        <v>-1.1091</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4932</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2783</v>
+        <v>-1.1941</v>
       </c>
       <c r="G21" t="n">
         <v>-1.1983</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4132</v>
+        <v>0.0893</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4932</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0799</v>
+        <v>0.0042</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>T. KOHAN LÓPEZ</t>
+          <t>D. LORAS MONTERO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.536</v>
+        <v>-2.3148</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.398</v>
+        <v>-1.3818</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1381</v>
+        <v>-0.9330000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.1517</v>
+        <v>-3.4128</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7203000000000001</v>
+        <v>-0.8606</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.872</v>
+        <v>-2.5522</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1008</v>
+        <v>-0.2374</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1008</v>
+        <v>-0.2048</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-0.0325</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.2525</v>
+        <v>-3.1755</v>
       </c>
       <c r="N22" t="n">
-        <v>0.6195000000000001</v>
+        <v>-0.6558</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.872</v>
+        <v>-2.5197</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-2.3806</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-4.9596</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.579</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3843</v>
+        <v>2.752</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4988</v>
+        <v>1.882</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1145</v>
+        <v>0.87</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.7267</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.9331</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.2945</v>
+        <v>-5.1637</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.0574</v>
+        <v>-5.3432</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2371</v>
+        <v>0.1795</v>
       </c>
       <c r="G23" t="n">
         <v>-4.9828</v>
@@ -2248,13 +2248,13 @@
         <v>1.9838</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6405</v>
+        <v>1.7713</v>
       </c>
       <c r="T23" t="n">
-        <v>0.822</v>
+        <v>1.5362</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1814</v>
+        <v>0.2352</v>
       </c>
       <c r="V23" t="n">
         <v>-1.9522</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>9.096099999999996</v>
+        <v>9.776299999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>15.8523</v>
+        <v>15.8522</v>
       </c>
       <c r="F24" t="n">
-        <v>-6.756299999999999</v>
+        <v>-6.0761</v>
       </c>
       <c r="G24" t="n">
         <v>-9.457799999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>3.303299999999999</v>
+        <v>3.3033</v>
       </c>
       <c r="I24" t="n">
         <v>-12.7613</v>
@@ -2302,7 +2302,7 @@
         <v>9.0021</v>
       </c>
       <c r="K24" t="n">
-        <v>7.189099999999999</v>
+        <v>7.189100000000001</v>
       </c>
       <c r="L24" t="n">
         <v>1.813</v>
@@ -2326,13 +2326,13 @@
         <v>14.8788</v>
       </c>
       <c r="S24" t="n">
-        <v>14.8507</v>
+        <v>15.531</v>
       </c>
       <c r="T24" t="n">
         <v>11.1955</v>
       </c>
       <c r="U24" t="n">
-        <v>3.6554</v>
+        <v>4.3355</v>
       </c>
       <c r="V24" t="n">
         <v>1.7196</v>
